--- a/output/pdf_financials_xlsx/CTV.xlsx
+++ b/output/pdf_financials_xlsx/CTV.xlsx
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.360642</v>
+        <v>-0.360642</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.360642</v>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.360642</v>
+        <v>-0.360642</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.360642</v>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.360642</v>
+        <v>-0.360642</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.360642</v>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.360642</v>
+        <v>-0.360642</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.360642</v>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.360642</v>
+        <v>-0.360642</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.360642</v>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -2893,16 +2893,16 @@
         <v>0.037586</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.092775</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.548578</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.954017</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.351529</v>
       </c>
     </row>
     <row r="93">
@@ -4840,7 +4840,11 @@
           <t>Reserves (note 11)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -5344,7 +5348,11 @@
           <t>Reserves (note 9)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -5822,7 +5830,11 @@
           <t>Reserves (note 10)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -12876,7 +12888,7 @@
         </is>
       </c>
       <c r="E193" s="5" t="n">
-        <v>0.360642</v>
+        <v>-0.360642</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CTV.xlsx
+++ b/output/pdf_financials_xlsx/CTV.xlsx
@@ -714,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.027401</v>
       </c>
     </row>
     <row r="13">
@@ -1080,13 +1080,13 @@
         <v>0.005314</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.005315</v>
+        <v>0.005314</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>58.467371</v>
+        <v>60.368511</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>78.48699999999999</v>
+        <v>78.670625</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>124.063892</v>
@@ -1117,7 +1117,7 @@
         <v>-14.887667</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.511869</v>
+        <v>-2.53927</v>
       </c>
     </row>
     <row r="28">
@@ -1167,7 +1167,7 @@
         <v>-14.887667</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.511869</v>
+        <v>-2.53927</v>
       </c>
     </row>
     <row r="30">
@@ -1291,16 +1291,16 @@
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.34373</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.053154</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.665845</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.998844</v>
       </c>
     </row>
     <row r="35">
@@ -1345,16 +1345,16 @@
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.34373</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.053154</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.665845</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.998844</v>
       </c>
     </row>
     <row r="37">
@@ -1669,16 +1669,16 @@
         <v>8.673344999999999</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.926592</v>
+        <v>1.582862</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.119015</v>
+        <v>2.065861</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.788751</v>
+        <v>0.122906</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.114361</v>
+        <v>0.115517</v>
       </c>
     </row>
     <row r="49">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">

--- a/output/pdf_financials_xlsx/CTV.xlsx
+++ b/output/pdf_financials_xlsx/CTV.xlsx
@@ -574,22 +574,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.13446</v>
+        <v>0.13846</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.13446</v>
+        <v>0.13846</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.134506</v>
+        <v>0.228622</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.089229</v>
+        <v>0.174629</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.19419</v>
+        <v>0.27979</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.215928</v>
+        <v>0.305528</v>
       </c>
     </row>
     <row r="8">
@@ -3485,13 +3485,13 @@
         <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.313977</v>
       </c>
       <c r="E116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.016056</v>
       </c>
       <c r="G116" s="3" t="n">
         <v>0</v>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>PurchaseOfIntangibles</t>
+          <t>NetIntangiblesPurchaseAndSale</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7876,7 +7876,11 @@
           <t>Proceeds from share issuance (note 11(b))</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -8290,7 +8294,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>PurchaseOfIntangibles</t>
+          <t>NetIntangiblesPurchaseAndSale</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8664,7 +8668,11 @@
           <t>Acquisition of intangible asset</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -8758,7 +8766,11 @@
           <t>Proceeds from share issuance (note 9(b))</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -9318,7 +9330,11 @@
           <t>Acquisition of intangible asset (note 6)</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -9364,7 +9380,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -10606,7 +10626,11 @@
           <t>Directors’ fee (note 12)</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -11810,7 +11834,11 @@
           <t>Directors’ fee (note 10)</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -12230,7 +12258,11 @@
           <t>Directors’ fee (note 11)</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -12648,7 +12680,11 @@
           <t>Directors fees 12</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E188" s="5" t="n">
         <v>0.004</v>
       </c>
